--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -856,7 +856,9 @@
       <c r="F11" t="n">
         <v>28.93</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>0.01321956768744587</v>
+      </c>
       <c r="H11" t="n">
         <v>35.59</v>
       </c>
@@ -3584,7 +3586,9 @@
       <c r="F79" t="n">
         <v>21.53</v>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>0.7563625783740417</v>
+      </c>
       <c r="H79" t="n">
         <v>54.93</v>
       </c>
